--- a/markets/invest_map/dist/20261025_AI投資地圖_資料_v0.3.xlsx
+++ b/markets/invest_map/dist/20261025_AI投資地圖_資料_v0.3.xlsx
@@ -517,7 +517,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>收支關卡（Andy 2026-10-25 10:48）：先看收支、再看評價。模型期間（2026 起約五年）現金收支合計為負＝入不敷出、有資金缺口，不論估值空間多大，最終分級一律為「收支不足」。口徑：有自由現金流列者用自由現金流；雲端／neocloud 模板無此列者用「營運缺口（不含融資、不含還本）」；只有損益的半導體模型以「各情境淨利皆為正」判定（現金流本專案未建立）。</t>
+          <t>收支關卡（Andy 2026-10-25 10:48）：先看收支、再看評價。模型期間（2026 起約五年）現金收支合計為負＝入不敷出、有資金缺口，不論估值空間多大，最終分級一律為「收支不足」。口徑：雲端／neocloud／MAG 模板一律用「營運缺口＋股東回饋（股利、回購）」；記憶體、模型商用自由現金流；只有損益的半導體模型以「各情境淨利皆為正」判定（現金流本專案未建立）。</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1883,7 +1883,7 @@
         <v/>
       </c>
       <c r="N2">
-        <f>RANK(M2,$M$2:$M$23,0)</f>
+        <f>RANK(M2,$M$2:$M$25,0)</f>
         <v/>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
         <v/>
       </c>
       <c r="N3">
-        <f>RANK(M3,$M$2:$M$23,0)</f>
+        <f>RANK(M3,$M$2:$M$25,0)</f>
         <v/>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
         <v/>
       </c>
       <c r="N4">
-        <f>RANK(M4,$M$2:$M$23,0)</f>
+        <f>RANK(M4,$M$2:$M$25,0)</f>
         <v/>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
         <v/>
       </c>
       <c r="N5">
-        <f>RANK(M5,$M$2:$M$23,0)</f>
+        <f>RANK(M5,$M$2:$M$25,0)</f>
         <v/>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         <v/>
       </c>
       <c r="N6">
-        <f>RANK(M6,$M$2:$M$23,0)</f>
+        <f>RANK(M6,$M$2:$M$25,0)</f>
         <v/>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
         <v/>
       </c>
       <c r="N7">
-        <f>RANK(M7,$M$2:$M$23,0)</f>
+        <f>RANK(M7,$M$2:$M$25,0)</f>
         <v/>
       </c>
     </row>
@@ -2249,7 +2249,7 @@
         <v/>
       </c>
       <c r="N8">
-        <f>RANK(M8,$M$2:$M$23,0)</f>
+        <f>RANK(M8,$M$2:$M$25,0)</f>
         <v/>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
         <v/>
       </c>
       <c r="N9">
-        <f>RANK(M9,$M$2:$M$23,0)</f>
+        <f>RANK(M9,$M$2:$M$25,0)</f>
         <v/>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
         <v/>
       </c>
       <c r="N10">
-        <f>RANK(M10,$M$2:$M$23,0)</f>
+        <f>RANK(M10,$M$2:$M$25,0)</f>
         <v/>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
         <v/>
       </c>
       <c r="N11">
-        <f>RANK(M11,$M$2:$M$23,0)</f>
+        <f>RANK(M11,$M$2:$M$25,0)</f>
         <v/>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
         <v/>
       </c>
       <c r="N12">
-        <f>RANK(M12,$M$2:$M$23,0)</f>
+        <f>RANK(M12,$M$2:$M$25,0)</f>
         <v/>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
         <v/>
       </c>
       <c r="N13">
-        <f>RANK(M13,$M$2:$M$23,0)</f>
+        <f>RANK(M13,$M$2:$M$25,0)</f>
         <v/>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
         <v/>
       </c>
       <c r="N14">
-        <f>RANK(M14,$M$2:$M$23,0)</f>
+        <f>RANK(M14,$M$2:$M$25,0)</f>
         <v/>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
         <v/>
       </c>
       <c r="N15">
-        <f>RANK(M15,$M$2:$M$23,0)</f>
+        <f>RANK(M15,$M$2:$M$25,0)</f>
         <v/>
       </c>
     </row>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="N16">
-        <f>RANK(M16,$M$2:$M$23,0)</f>
+        <f>RANK(M16,$M$2:$M$25,0)</f>
         <v/>
       </c>
     </row>
@@ -2798,7 +2798,7 @@
         <v/>
       </c>
       <c r="N17">
-        <f>RANK(M17,$M$2:$M$23,0)</f>
+        <f>RANK(M17,$M$2:$M$25,0)</f>
         <v/>
       </c>
     </row>
@@ -2859,7 +2859,7 @@
         <v/>
       </c>
       <c r="N18">
-        <f>RANK(M18,$M$2:$M$23,0)</f>
+        <f>RANK(M18,$M$2:$M$25,0)</f>
         <v/>
       </c>
     </row>
@@ -2920,7 +2920,7 @@
         <v/>
       </c>
       <c r="N19">
-        <f>RANK(M19,$M$2:$M$23,0)</f>
+        <f>RANK(M19,$M$2:$M$25,0)</f>
         <v/>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
         <v/>
       </c>
       <c r="N20">
-        <f>RANK(M20,$M$2:$M$23,0)</f>
+        <f>RANK(M20,$M$2:$M$25,0)</f>
         <v/>
       </c>
     </row>
@@ -3042,19 +3042,19 @@
         <v/>
       </c>
       <c r="N21">
-        <f>RANK(M21,$M$2:$M$23,0)</f>
+        <f>RANK(M21,$M$2:$M$25,0)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00100</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C22">
@@ -3067,14 +3067,14 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>中國第二梯隊模型商；多模態、海外營收占比高</t>
+          <t>ChatGPT 與 API 用量最大的模型商；算力承諾最大（本專案 OpenAI 模型）</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3103,19 +3103,19 @@
         <v/>
       </c>
       <c r="N22">
-        <f>RANK(M22,$M$2:$M$23,0)</f>
+        <f>RANK(M22,$M$2:$M$25,0)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>02513</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>智譜</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C23">
@@ -3128,14 +3128,14 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
-          <t>中國第二梯隊模型商；政企本地化部署</t>
+          <t>企業與程式開發用途為主的前沿模型商（本專案 Anthropic 模型）</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3164,7 +3164,129 @@
         <v/>
       </c>
       <c r="N23">
-        <f>RANK(M23,$M$2:$M$23,0)</f>
+        <f>RANK(M23,$M$2:$M$25,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>00100</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MiniMax</t>
+        </is>
+      </c>
+      <c r="C24">
+        <f>價值鏈!A2</f>
+        <v/>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AI 模型商</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>中國第二梯隊模型商；多模態、海外營收占比高</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>[判斷]</t>
+        </is>
+      </c>
+      <c r="I24">
+        <f>價值鏈!F2</f>
+        <v/>
+      </c>
+      <c r="J24">
+        <f>價值鏈!G2</f>
+        <v/>
+      </c>
+      <c r="K24">
+        <f>(CHOOSE(I24,s_irr1,s_irr2,s_irr3)+CHOOSE(E24,s_irr1,s_irr2,s_irr3))/2</f>
+        <v/>
+      </c>
+      <c r="L24">
+        <f>CHOOSE(F24,s_pos1,s_pos2,s_pos3,s_pos4)</f>
+        <v/>
+      </c>
+      <c r="M24">
+        <f>w_irr*K24+w_pos*L24+w_vc*J24</f>
+        <v/>
+      </c>
+      <c r="N24">
+        <f>RANK(M24,$M$2:$M$25,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>02513</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>智譜</t>
+        </is>
+      </c>
+      <c r="C25">
+        <f>價值鏈!A2</f>
+        <v/>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AI 模型商</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>中國第二梯隊模型商；政企本地化部署</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>[判斷]</t>
+        </is>
+      </c>
+      <c r="I25">
+        <f>價值鏈!F2</f>
+        <v/>
+      </c>
+      <c r="J25">
+        <f>價值鏈!G2</f>
+        <v/>
+      </c>
+      <c r="K25">
+        <f>(CHOOSE(I25,s_irr1,s_irr2,s_irr3)+CHOOSE(E25,s_irr1,s_irr2,s_irr3))/2</f>
+        <v/>
+      </c>
+      <c r="L25">
+        <f>CHOOSE(F25,s_pos1,s_pos2,s_pos3,s_pos4)</f>
+        <v/>
+      </c>
+      <c r="M25">
+        <f>w_irr*K25+w_pos*L25+w_vc*J25</f>
+        <v/>
+      </c>
+      <c r="N25">
+        <f>RANK(M25,$M$2:$M$25,0)</f>
         <v/>
       </c>
     </row>
@@ -3179,7 +3301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4037,6 +4159,44 @@
         <v/>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>未上市</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>未上市</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4048,7 +4208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI23"/>
+  <dimension ref="A1:AI25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4363,23 +4523,23 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>PL 頁各情境淨利</t>
+          <t>PL 頁各情境模型年度淨利（不含實績）</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>35 個情境年度淨利，全部 為正</t>
+          <t>12 個情境年度淨利（不含實績），全部為正</t>
         </is>
       </c>
       <c r="AE2" s="4" t="n">
-        <v>9831.987212663698</v>
+        <v>4314.771494494909</v>
       </c>
       <c r="AF2" s="4" t="n">
-        <v>112.494809527772</v>
+        <v>219.760389832454</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>[Derived] nvidia/dist/20261023_NVIDIA模型_v0.1.1.xlsx PL!C12…PL!G292</t>
+          <t>[Derived] nvidia/dist/20261023_NVIDIA模型_v0.1.1.xlsx PL!D12…PL!G292</t>
         </is>
       </c>
       <c r="AH2">
@@ -4387,7 +4547,7 @@
         <v/>
       </c>
       <c r="AI2">
-        <f>IF(AH2="不通過","收支不足",S2)</f>
+        <f>IF(S2="未上市","未上市",IF(AH2="不通過","收支不足",S2))</f>
         <v/>
       </c>
     </row>
@@ -4481,23 +4641,23 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>PL 頁各情境淨利</t>
+          <t>PL 頁各情境模型年度淨利（不含實績）</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>30 個情境年度淨利，全部 為正</t>
+          <t>8 個情境年度淨利（不含實績），全部為正</t>
         </is>
       </c>
       <c r="AE3" s="4" t="n">
-        <v>2210.188539951681</v>
+        <v>711.2280417774298</v>
       </c>
       <c r="AF3" s="4" t="n">
-        <v>33.728</v>
+        <v>57.42012</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>[Derived] ../../../tmp/claude-0/avgo/avgo/dist/20261023_Broadcom模型_v0.1.xlsx PL!C13…PL!G229</t>
+          <t>[Derived] ../../../tmp/claude-0/avgo/avgo/dist/20261023_Broadcom模型_v0.1.xlsx PL!D13…PL!G39</t>
         </is>
       </c>
       <c r="AH3">
@@ -4505,7 +4665,7 @@
         <v/>
       </c>
       <c r="AI3">
-        <f>IF(AH3="不通過","收支不足",S3)</f>
+        <f>IF(S3="未上市","未上市",IF(AH3="不通過","收支不足",S3))</f>
         <v/>
       </c>
     </row>
@@ -4635,7 +4795,7 @@
         <v/>
       </c>
       <c r="AI4">
-        <f>IF(AH4="不通過","收支不足",S4)</f>
+        <f>IF(S4="未上市","未上市",IF(AH4="不通過","收支不足",S4))</f>
         <v/>
       </c>
     </row>
@@ -4765,7 +4925,7 @@
         <v/>
       </c>
       <c r="AI5">
-        <f>IF(AH5="不通過","收支不足",S5)</f>
+        <f>IF(S5="未上市","未上市",IF(AH5="不通過","收支不足",S5))</f>
         <v/>
       </c>
     </row>
@@ -4895,7 +5055,7 @@
         <v/>
       </c>
       <c r="AI6">
-        <f>IF(AH6="不通過","收支不足",S6)</f>
+        <f>IF(S6="未上市","未上市",IF(AH6="不通過","收支不足",S6))</f>
         <v/>
       </c>
     </row>
@@ -5008,12 +5168,12 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>PL 頁各情境淨利</t>
+          <t>PL 頁各情境模型年度淨利（不含實績）</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>10 個情境年度淨利，全部 為正</t>
+          <t>10 個情境年度淨利（不含實績），全部為正</t>
         </is>
       </c>
       <c r="AE7" s="4" t="n">
@@ -5032,7 +5192,7 @@
         <v/>
       </c>
       <c r="AI7">
-        <f>IF(AH7="不通過","收支不足",S7)</f>
+        <f>IF(S7="未上市","未上市",IF(AH7="不通過","收支不足",S7))</f>
         <v/>
       </c>
     </row>
@@ -5138,23 +5298,23 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>PL 頁各情境淨利</t>
+          <t>PL 頁各情境模型年度淨利（不含實績）</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>30 個情境年度淨利，全部 為正</t>
+          <t>8 個情境年度淨利（不含實績），全部為正</t>
         </is>
       </c>
       <c r="AE8" s="4" t="n">
-        <v>184.2094367559607</v>
+        <v>56.29032871517846</v>
       </c>
       <c r="AF8" s="4" t="n">
-        <v>3.806</v>
+        <v>5.224907</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>[Derived] arista/dist/20261024_Arista模型_v0.1.xlsx PL!C12…PL!G147</t>
+          <t>[Derived] arista/dist/20261024_Arista模型_v0.1.xlsx PL!D12…PL!G36</t>
         </is>
       </c>
       <c r="AH8">
@@ -5162,7 +5322,7 @@
         <v/>
       </c>
       <c r="AI8">
-        <f>IF(AH8="不通過","收支不足",S8)</f>
+        <f>IF(S8="未上市","未上市",IF(AH8="不通過","收支不足",S8))</f>
         <v/>
       </c>
     </row>
@@ -5272,23 +5432,23 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>PL 頁各情境淨利</t>
+          <t>PL 頁各情境模型年度淨利（不含實績）</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>30 個情境年度淨利，全部 為正</t>
+          <t>8 個情境年度淨利（不含實績），全部為正</t>
         </is>
       </c>
       <c r="AE9" s="4" t="n">
-        <v>1214.705294278893</v>
+        <v>399.9561705197759</v>
       </c>
       <c r="AF9" s="4" t="n">
-        <v>10.797</v>
+        <v>31.8281188474012</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>[Derived] innolight/dist/20261024_中際旭創模型_v0.1.xlsx PL!C12…PL!G149</t>
+          <t>[Derived] innolight/dist/20261024_中際旭創模型_v0.1.xlsx PL!D12…PL!G36</t>
         </is>
       </c>
       <c r="AH9">
@@ -5296,7 +5456,7 @@
         <v/>
       </c>
       <c r="AI9">
-        <f>IF(AH9="不通過","收支不足",S9)</f>
+        <f>IF(S9="未上市","未上市",IF(AH9="不通過","收支不足",S9))</f>
         <v/>
       </c>
     </row>
@@ -5402,23 +5562,23 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>PL 頁各情境淨利</t>
+          <t>PL 頁各情境模型年度淨利（不含實績）</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>30 個情境年度淨利，全部 為正</t>
+          <t>8 個情境年度淨利（不含實績），全部為正</t>
         </is>
       </c>
       <c r="AE10" s="4" t="n">
-        <v>4047.392536240182</v>
+        <v>1331.031109556913</v>
       </c>
       <c r="AF10" s="4" t="n">
-        <v>60.108</v>
+        <v>98.429235925</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>[Derived] delta/dist/20261024_台達電模型_v0.1.xlsx PL!C13…PL!G171</t>
+          <t>[Derived] delta/dist/20261024_台達電模型_v0.1.xlsx PL!D13…PL!G39</t>
         </is>
       </c>
       <c r="AH10">
@@ -5426,7 +5586,7 @@
         <v/>
       </c>
       <c r="AI10">
-        <f>IF(AH10="不通過","收支不足",S10)</f>
+        <f>IF(S10="未上市","未上市",IF(AH10="不通過","收支不足",S10))</f>
         <v/>
       </c>
     </row>
@@ -5532,23 +5692,23 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>PL 頁各情境淨利</t>
+          <t>PL 頁各情境模型年度淨利（不含實績）</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>30 個情境年度淨利，全部 為正</t>
+          <t>8 個情境年度淨利（不含實績），全部為正</t>
         </is>
       </c>
       <c r="AE11" s="4" t="n">
-        <v>4153.221447696762</v>
+        <v>1294.029322125413</v>
       </c>
       <c r="AF11" s="4" t="n">
-        <v>74.98</v>
+        <v>110.713671625</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>[Derived] quanta/dist/20261024_廣達模型_v0.1.xlsx PL!C13…PL!G171</t>
+          <t>[Derived] quanta/dist/20261024_廣達模型_v0.1.xlsx PL!D13…PL!G39</t>
         </is>
       </c>
       <c r="AH11">
@@ -5556,7 +5716,7 @@
         <v/>
       </c>
       <c r="AI11">
-        <f>IF(AH11="不通過","收支不足",S11)</f>
+        <f>IF(S11="未上市","未上市",IF(AH11="不通過","收支不足",S11))</f>
         <v/>
       </c>
     </row>
@@ -5650,23 +5810,23 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>PL 頁各情境淨利</t>
+          <t>PL 頁各情境模型年度淨利（不含實績）</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>30 個情境年度淨利，全部 為正</t>
+          <t>8 個情境年度淨利（不含實績），全部為正</t>
         </is>
       </c>
       <c r="AE12" s="4" t="n">
-        <v>2912.837454335999</v>
+        <v>854.6935870581774</v>
       </c>
       <c r="AF12" s="4" t="n">
-        <v>63.713</v>
+        <v>84</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>[Derived] ibiden/dist/20261024_Ibiden模型_v0.1.xlsx PL!C11…PL!G156</t>
+          <t>[Derived] ibiden/dist/20261024_Ibiden模型_v0.1.xlsx PL!D11…PL!G33</t>
         </is>
       </c>
       <c r="AH12">
@@ -5674,7 +5834,7 @@
         <v/>
       </c>
       <c r="AI12">
-        <f>IF(AH12="不通過","收支不足",S12)</f>
+        <f>IF(S12="未上市","未上市",IF(AH12="不通過","收支不足",S12))</f>
         <v/>
       </c>
     </row>
@@ -5759,23 +5919,23 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>PL 頁各情境淨利</t>
+          <t>PL 頁各情境模型年度淨利（不含實績）</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>30 個情境年度淨利，全部 為正</t>
+          <t>10 個情境年度淨利（不含實績），全部為正</t>
         </is>
       </c>
       <c r="AE13" s="4" t="n">
-        <v>20374.08496527686</v>
+        <v>7834.34551344892</v>
       </c>
       <c r="AF13" s="4" t="n">
-        <v>375.4</v>
+        <v>574.3864027252999</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>[Derived] advantest/dist/20261023_Advantest模型_v0.2.2.xlsx PL!C12…PL!G122</t>
+          <t>[Derived] advantest/dist/20261023_Advantest模型_v0.2.2.xlsx PL!D12…PL!G34</t>
         </is>
       </c>
       <c r="AH13">
@@ -5783,7 +5943,7 @@
         <v/>
       </c>
       <c r="AI13">
-        <f>IF(AH13="不通過","收支不足",S13)</f>
+        <f>IF(S13="未上市","未上市",IF(AH13="不通過","收支不足",S13))</f>
         <v/>
       </c>
     </row>
@@ -5868,23 +6028,23 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>PL 頁各情境淨利</t>
+          <t>PL 頁各情境模型年度淨利（不含實績）</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>30 個情境年度淨利，全部 為正</t>
+          <t>10 個情境年度淨利（不含實績），全部為正</t>
         </is>
       </c>
       <c r="AE14" s="4" t="n">
-        <v>5014.645076769742</v>
+        <v>1764.840775606191</v>
       </c>
       <c r="AF14" s="4" t="n">
-        <v>135.521</v>
+        <v>143.891188584055</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>[Derived] disco/dist/20261023_Disco模型_v0.1.3.xlsx PL!C16…PL!G244</t>
+          <t>[Derived] disco/dist/20261023_Disco模型_v0.1.3.xlsx PL!D16…PL!G52</t>
         </is>
       </c>
       <c r="AH14">
@@ -5892,7 +6052,7 @@
         <v/>
       </c>
       <c r="AI14">
-        <f>IF(AH14="不通過","收支不足",S14)</f>
+        <f>IF(S14="未上市","未上市",IF(AH14="不通過","收支不足",S14))</f>
         <v/>
       </c>
     </row>
@@ -5989,23 +6149,23 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>自由現金流（FCF＝營運現金 − 現金資本支出）</t>
+          <t>營運缺口＋股利＋回購（營運缺口加回股東回饋）</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>FY27 1.2、FY28 37.2、FY29 80.5、FY30 88.3、FY31 23.3</t>
+          <t>FY27 -7.8、FY28 27.7、FY29 70.2、FY30 76.7、FY31 11.2</t>
         </is>
       </c>
       <c r="AE15" s="4" t="n">
-        <v>230.4767517004849</v>
+        <v>178.0401267004849</v>
       </c>
       <c r="AF15" s="4" t="n">
-        <v>1.24629259914113</v>
+        <v>-7.831738650858899</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>[Derived] microsoft/dist/20261025_Microsoft收支模型_v0_2_2.xlsx 各期收支!C44…各期收支!G44</t>
+          <t>[Derived] microsoft/dist/20261025_Microsoft收支模型_v0_2_2.xlsx 各期收支!C54＋C23＋C24…各期收支!G54＋G23＋G24</t>
         </is>
       </c>
       <c r="AH15">
@@ -6013,7 +6173,7 @@
         <v/>
       </c>
       <c r="AI15">
-        <f>IF(AH15="不通過","收支不足",S15)</f>
+        <f>IF(S15="未上市","未上市",IF(AH15="不通過","收支不足",S15))</f>
         <v/>
       </c>
     </row>
@@ -6110,23 +6270,23 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>自由現金流（FCF＝營運現金 − 現金資本支出）</t>
+          <t>營運缺口＋股利＋回購（營運缺口加回股東回饋）</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2026 -60.0、2027 -67.6、2028 -29.8、2029 10.0、2030 -66.4</t>
+          <t>2026 -122.8、2027 -71.8、2028 -34.2、2029 6.1、2030 -70.1</t>
         </is>
       </c>
       <c r="AE16" s="4" t="n">
-        <v>-213.784581805032</v>
+        <v>-292.8415771813029</v>
       </c>
       <c r="AF16" s="4" t="n">
-        <v>-67.6423913811975</v>
+        <v>-122.819739543556</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>[Derived] amazon/dist/20261025_Amazon收支模型_v0_2_2.xlsx 各期收支!C44…各期收支!G44</t>
+          <t>[Derived] amazon/dist/20261025_Amazon收支模型_v0_2_2.xlsx 各期收支!C54＋C23＋C24…各期收支!G54＋G23＋G24</t>
         </is>
       </c>
       <c r="AH16">
@@ -6134,7 +6294,7 @@
         <v/>
       </c>
       <c r="AI16">
-        <f>IF(AH16="不通過","收支不足",S16)</f>
+        <f>IF(S16="未上市","未上市",IF(AH16="不通過","收支不足",S16))</f>
         <v/>
       </c>
     </row>
@@ -6231,23 +6391,23 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>自由現金流（FCF＝營運現金 − 現金資本支出）</t>
+          <t>營運缺口＋股利＋回購（營運缺口加回股東回饋）</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2026 -4.1、2027 -6.4、2028 16.0、2029 28.3、2030 -62.3</t>
+          <t>2026 -62.0、2027 -11.4、2028 10.9、2029 23.1、2030 -67.6</t>
         </is>
       </c>
       <c r="AE17" s="4" t="n">
-        <v>-28.49105701735244</v>
+        <v>-106.9279391300797</v>
       </c>
       <c r="AF17" s="4" t="n">
-        <v>-62.3373425541111</v>
+        <v>-67.601689194111</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>[Derived] alphabet/dist/20261025_Alphabet收支模型_v0_2_2.xlsx 各期收支!C44…各期收支!G44</t>
+          <t>[Derived] alphabet/dist/20261025_Alphabet收支模型_v0_2_2.xlsx 各期收支!C54＋C23＋C24…各期收支!G54＋G23＋G24</t>
         </is>
       </c>
       <c r="AH17">
@@ -6255,7 +6415,7 @@
         <v/>
       </c>
       <c r="AI17">
-        <f>IF(AH17="不通過","收支不足",S17)</f>
+        <f>IF(S17="未上市","未上市",IF(AH17="不通過","收支不足",S17))</f>
         <v/>
       </c>
     </row>
@@ -6352,23 +6512,23 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>營運缺口（不含融資、不含還本）</t>
+          <t>營運缺口＋股利（營運缺口加回股東回饋）</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>FY27 -32.1、FY28 -27.5、FY29 17.4、FY30 3.6、FY31 2.0</t>
+          <t>FY27 -25.8、FY28 -21.1、FY29 23.7、FY30 9.7、FY31 8.1</t>
         </is>
       </c>
       <c r="AE18" s="4" t="n">
-        <v>-36.65954451431514</v>
+        <v>-5.431099371743606</v>
       </c>
       <c r="AF18" s="4" t="n">
-        <v>-32.1477872210438</v>
+        <v>-25.8031832210438</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>[Derived] oracle/dist/20261022_Oracle收支模型_v0_3_1.xlsx 各期收支!C50…各期收支!G50</t>
+          <t>[Derived] oracle/dist/20261022_Oracle收支模型_v0_3_1.xlsx 各期收支!C50＋C23…各期收支!G50＋G23</t>
         </is>
       </c>
       <c r="AH18">
@@ -6376,7 +6536,7 @@
         <v/>
       </c>
       <c r="AI18">
-        <f>IF(AH18="不通過","收支不足",S18)</f>
+        <f>IF(S18="未上市","未上市",IF(AH18="不通過","收支不足",S18))</f>
         <v/>
       </c>
     </row>
@@ -6473,7 +6633,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>營運缺口（不含融資、不含還本）</t>
+          <t>營運缺口（營運缺口加回股東回饋）</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -6497,7 +6657,7 @@
         <v/>
       </c>
       <c r="AI19">
-        <f>IF(AH19="不通過","收支不足",S19)</f>
+        <f>IF(S19="未上市","未上市",IF(AH19="不通過","收支不足",S19))</f>
         <v/>
       </c>
     </row>
@@ -6594,7 +6754,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>營運缺口（不含融資、不含還本）</t>
+          <t>營運缺口（營運缺口加回股東回饋）</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -6618,7 +6778,7 @@
         <v/>
       </c>
       <c r="AI20">
-        <f>IF(AH20="不通過","收支不足",S20)</f>
+        <f>IF(S20="未上市","未上市",IF(AH20="不通過","收支不足",S20))</f>
         <v/>
       </c>
     </row>
@@ -6715,7 +6875,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>營運缺口（不含融資、不含還本）</t>
+          <t>營運缺口＋股利（營運缺口加回股東回饋）</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -6731,7 +6891,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>[Derived] whitefiber/dist/20261022_WhiteFiber收支模型_v0_2.xlsx 各期收支!C52…各期收支!G52</t>
+          <t>[Derived] whitefiber/dist/20261022_WhiteFiber收支模型_v0_2.xlsx 各期收支!C52＋C24…各期收支!G52＋G24</t>
         </is>
       </c>
       <c r="AH21">
@@ -6739,7 +6899,7 @@
         <v/>
       </c>
       <c r="AI21">
-        <f>IF(AH21="不通過","收支不足",S21)</f>
+        <f>IF(S21="未上市","未上市",IF(AH21="不通過","收支不足",S21))</f>
         <v/>
       </c>
     </row>
@@ -6829,23 +6989,23 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>F06</t>
+          <t>F06 營運燒錢（經調整淨利）＋F07 算力預付與自建資本支出</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>FY2026 -578.3、FY2027 -826.5、FY2028 -1,129.9、FY2029 -1,433.3、FY2030 -1,693.3</t>
+          <t>FY2026 -900.3、FY2027 -826.5、FY2028 -1,129.9、FY2029 -1,433.3、FY2030 -1,693.3</t>
         </is>
       </c>
       <c r="AE22" s="4" t="n">
-        <v>-5661.185548552452</v>
+        <v>-5983.185548552452</v>
       </c>
       <c r="AF22" s="4" t="n">
         <v>-1693.27864140096</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>[Derived] minimax/dist/20261022_MiniMax收支模型_v0_2.xlsx Funding!E13…Funding!I13</t>
+          <t>[Derived] minimax/dist/20261022_MiniMax收支模型_v0_2.xlsx Funding!E13＋E14…Funding!I13＋I14</t>
         </is>
       </c>
       <c r="AH22">
@@ -6853,7 +7013,7 @@
         <v/>
       </c>
       <c r="AI22">
-        <f>IF(AH22="不通過","收支不足",S22)</f>
+        <f>IF(S22="未上市","未上市",IF(AH22="不通過","收支不足",S22))</f>
         <v/>
       </c>
     </row>
@@ -6911,7 +7071,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>F09</t>
+          <t>F09 自由現金流</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -6935,7 +7095,171 @@
         <v/>
       </c>
       <c r="AI23">
-        <f>IF(AH23="不通過","收支不足",S23)</f>
+        <f>IF(S23="未上市","未上市",IF(AH23="不通過","收支不足",S23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C24">
+        <f>價值鏈!A2</f>
+        <v/>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AI 模型商</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>未上市</t>
+        </is>
+      </c>
+      <c r="N24">
+        <f>價格!H24</f>
+        <v/>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>未上市</t>
+        </is>
+      </c>
+      <c r="W24" s="1" t="inlineStr">
+        <is>
+          <t>未上市：不評估可投資性；收支關卡結果只作參考。</t>
+        </is>
+      </c>
+      <c r="Z24">
+        <f>IF(ISNUMBER(價格!C24),價格!H24/價格!C24-1,"")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>IF(Z24="","",IF(ABS(Z24)&gt;0.2,"模型尚未反映期間變化",""))</f>
+        <v/>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>現金流</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>F06 自由現金流</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>2026 -39.4、2027 -116.0、2028 -134.9、2029 -137.6、2030 -131.9</t>
+        </is>
+      </c>
+      <c r="AE24" s="4" t="n">
+        <v>-559.844811653528</v>
+      </c>
+      <c r="AF24" s="4" t="n">
+        <v>-137.624622192723</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>[Derived] openai/dist/20261025_OpenAI收支模型_v0_6_3.xlsx Funding!E13…Funding!I13</t>
+        </is>
+      </c>
+      <c r="AH24">
+        <f>IF(AB24="淨利",IF(AF24&gt;0,"通過（淨利）","不通過"),IF(AE24&lt;0,"不通過","通過（現金流）"))</f>
+        <v/>
+      </c>
+      <c r="AI24">
+        <f>IF(S24="未上市","未上市",IF(AH24="不通過","收支不足",S24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C25">
+        <f>價值鏈!A2</f>
+        <v/>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AI 模型商</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>未上市</t>
+        </is>
+      </c>
+      <c r="N25">
+        <f>價格!H25</f>
+        <v/>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>未上市</t>
+        </is>
+      </c>
+      <c r="W25" s="1" t="inlineStr">
+        <is>
+          <t>未上市：不評估可投資性；收支關卡結果只作參考。</t>
+        </is>
+      </c>
+      <c r="Z25">
+        <f>IF(ISNUMBER(價格!C25),價格!H25/價格!C25-1,"")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>IF(Z25="","",IF(ABS(Z25)&gt;0.2,"模型尚未反映期間變化",""))</f>
+        <v/>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>現金流</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>F07 自由現金流</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>2026 -2.6、2027 -18.5、2028 -15.0、2029 47.6、2030 96.1</t>
+        </is>
+      </c>
+      <c r="AE25" s="4" t="n">
+        <v>107.6782012460332</v>
+      </c>
+      <c r="AF25" s="4" t="n">
+        <v>-18.5037194506051</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>[Derived] anthropic/dist/20261024_Anthropic收支模型_v0_1_5.xlsx Funding!E14…Funding!I14</t>
+        </is>
+      </c>
+      <c r="AH25">
+        <f>IF(AB25="淨利",IF(AF25&gt;0,"通過（淨利）","不通過"),IF(AE25&lt;0,"不通過","通過（現金流）"))</f>
+        <v/>
+      </c>
+      <c r="AI25">
+        <f>IF(S25="未上市","未上市",IF(AH25="不通過","收支不足",S25))</f>
         <v/>
       </c>
     </row>
@@ -10440,26 +10764,26 @@
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>00100</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>港</t>
+          <t>未上市</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>中國第二梯隊模型商；多模態、海外營收占比高</t>
+          <t>ChatGPT 與 API 用量最大的模型商；算力承諾最大（本專案 OpenAI 模型）</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -10482,26 +10806,26 @@
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>智譜</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>02513</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>港</t>
+          <t>未上市</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>中國第二梯隊模型商；政企本地化部署</t>
+          <t>企業與程式開發用途為主的前沿模型商（本專案 Anthropic 模型）</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -10524,22 +10848,36 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>MiniMax</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>00100</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>未上市</t>
+          <t>港</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
+      <c r="G71" t="n">
+        <v>3</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>中國第二梯隊模型商；多模態、海外營收占比高</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>[判斷]</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>company-models openai v0.6.3（P×Q 回本比值）</t>
+          <t>有模型</t>
         </is>
       </c>
     </row>
@@ -10552,22 +10890,36 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>智譜</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>02513</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>未上市</t>
+          <t>港</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
+      <c r="G72" t="n">
+        <v>3</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>中國第二梯隊模型商；政企本地化部署</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>[判斷]</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>company-models anthropic v0.1.5</t>
+          <t>有模型</t>
         </is>
       </c>
     </row>
